--- a/agriculture 23.xlsx
+++ b/agriculture 23.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve">2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics  and Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -292,8 +295,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O25"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1347,28 +1350,47 @@
         <v>3.56155064849044</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A24:N24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A25:N25"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 23.xlsx
+++ b/agriculture 23.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics  and Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -296,7 +296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/agriculture 23.xlsx
+++ b/agriculture 23.xlsx
@@ -133,7 +133,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:Directorate of Economics  and Statistics( APY statistics 1998-99 to 2019-20)</t>
@@ -296,7 +296,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" s="2" customFormat="true" ht="46.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
